--- a/01_경혈별_해부생리_분석보고서/LU_수태음폐경/LU06_공최/LU06_공최_해부생리_분석데이터.xlsx
+++ b/01_경혈별_해부생리_분석보고서/LU_수태음폐경/LU06_공최/LU06_공최_해부생리_분석데이터.xlsx
@@ -17,6 +17,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LayerA_papers" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외부검색로그" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="개정이력" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FMA_해부실체" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -620,7 +621,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -840,6 +841,728 @@
       <c r="D10" t="inlineStr">
         <is>
           <t>WRITER_BRIEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>FMA_해부실체 시트 신설 (2026-10-23)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>FMA 5.1.0 실체 ID·지배신경·줄기·분절·교재 비교 추가, '깊은엄지굽힘근'→긴엄지굽힘근 정정. T1 71.2 ± 0 (B)·T2 35 ± 0 (D·H) 불변</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>fma_query.py profile LU06; 보고서 4·6·8절·부록 A</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="48" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="44" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="8" max="8"/>
+    <col width="28" customWidth="1" min="9" max="9"/>
+    <col width="50" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>교재 용어</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>FMA_ID</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>FMA_label</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>대응 수준</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>출처 교재</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>지배신경(FMA nerve_supply)</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>상위 줄기(FMA)</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>척수 분절(FMA segmental_supply)</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>근육</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>위팔노근 (brachioradialis)</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>38485</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Brachioradialis</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>공통교재·김재효</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>FMA:65334 Nerve to brachioradialis</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Peripheral segment of radial nerve</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>C6(primary/segmental), C5(secondary/segmental)</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>근육</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>노쪽손목굽힘근 (Flexor carpi radialis); 노쪽손목굽힘근 (flexor carpi radialis)</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>38459</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Flexor carpi radialis</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>공통교재·김재효</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>FMA:44824 Nerve to flexor carpi radialis</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Peripheral segment of median nerve</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>C6(primary/segmental), C7(secondary/segmental)</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>근육</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>자쪽손목굽힘근 (Flexor carpi ulnaris)</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>38465</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Flexor carpi ulnaris</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>공통교재</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>FMA:81220 Nerve to flexor carpi ulnaris</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Peripheral segment of ulnar nerve</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>C8(primary/segmental), C7(secondary/segmental), T1(secondary/segmental)</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>자신경 지배·자쪽 구조 — 공통교재 단독</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>근육</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>얕은손가락굽힘근 (flexor digitorum superficialis)</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>38469</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Flexor digitorum superficialis</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>김재효</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>FMA:44826 Nerve to flexor digitorum superficialis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Peripheral segment of median nerve</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>C8(primary/segmental), T1(secondary/segmental)</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>근육</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>깊은엄지굽힘근 (flexor pollicis longus)</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>38481</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Flexor pollicis longus</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>김재효</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>FMA:44830 Nerve to flexor pollicis longus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Anterior interosseous nerve → Peripheral segment of median nerve</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>C8(primary/segmental), C7(secondary/segmental)</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>교재 표기 '깊은엄지굽힘근'은 긴엄지굽힘근의 오기</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>근육</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>긴손바닥근 (palmaris longus)</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>38462</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Palmaris longus</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>공통교재</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>FMA:44825 Nerve to palmaris longus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Peripheral segment of median nerve</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>C7(segmental), C8(segmental)</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>근육</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>원엎침근 (pronator teres)</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>38450</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Pronator teres</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>공통교재·김재효</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>FMA:44823 Nerve to pronator teres</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Peripheral segment of median nerve</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>C7(primary/segmental), C6(secondary/segmental)</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>신경</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>가쪽아래팔피부신경 (lateral antebrachial cutaneous nerve)</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>39080</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Lateral cutaneous nerve of forearm</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>공통교재·김재효</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>FMA:288511 Peripheral segment of musculocutaneous nerve</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>FMA 미기재</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>신경</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>노신경의 얕은가지 (superficial branch of radial nerve); 노신경의 얕은가지 (superficial branch of the radial nerve)</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>292885</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Superficial branch of radial nerve</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>공통교재·김재효</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>FMA:37069 Radial nerve</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>FMA 미기재</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>혈관</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>덧노쪽피부정맥 (accessory cephalic vein)</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>22970</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Accessory cephalic vein</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>공통교재·김재효</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>FMA:13324 Cephalic vein → FMA:4725 Subclavian vein → FMA:4723 Brachiocephalic vein</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>FMA 미기재</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>혈관</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>노쪽피부정맥 (cephalic vein)</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>13324</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Cephalic vein</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>공통교재·김재효</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>FMA:4725 Subclavian vein → FMA:4723 Brachiocephalic vein</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>FMA 미기재</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>혈관</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>노동ㆍ정맥 (radial artery and vein)</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>22730</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Radial artery</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>공통교재·김재효</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>FMA:3951 Subclavian artery</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>FMA 미기재</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>FMA는 위팔동맥을 빗장밑동맥 구간으로 모델링</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>혈관</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>노동ㆍ정맥 (radial artery and vein)</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>22947</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Radial vein</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>공통교재·김재효</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>FMA:22934 Brachial vein → FMA:13329 Axillary vein → FMA:4725 Subclavian vein → FMA:4723 Brachiocephalic vein</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>FMA 미기재</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>분절 합집합</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>C5, C6, C7, C8, T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>교재 비교</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>공통 9 · 공통교재 단독 2 · 김재효 단독 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>출처</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>FMA 5.1.0 로컬 색인, fma_query.py profile LU06 (2026-10-23). B1 보조(등록부 미등재)</t>
         </is>
       </c>
     </row>
@@ -3198,7 +3921,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3363,6 +4086,103 @@
         <v>0</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-10-23T21:44:38</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>pubmed</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>200</v>
+      </c>
+      <c r="D6" t="n">
+        <v>9</v>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>("LU6" OR "Kongzui" OR "孔最") AND (acupuncture OR electroacupuncture) AND (nerve OR reflex OR autonomic OR mechanism OR anatomy) | ("LU6" OR "Kongzui" OR "孔最") AND ("Zhongguo Zhen Jiu"[Journal] OR "Zhen Ci Yan Jiu"[Journal])</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-10-23T21:44:38</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>openalex</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>200</v>
+      </c>
+      <c r="D7" t="n">
+        <v>16</v>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>doi_starts_with:10.13703,title_and_abstract.search:"Kongzui" OR "LU6" | doi_starts_with:10.13702,title_and_abstract.search:"Kongzui" OR "LU6" | has_doi:true,title_and_abstract.search:"Kongzui" OR "LU6" AND (acupuncture OR electroacupuncture)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-10-23T21:44:38</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>crossref</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>200</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Kongzui acupuncture nerve reflex</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-10-23T21:44:38</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>25</v>
+      </c>
+      <c r="E9" t="n">
+        <v>25</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/01_경혈별_해부생리_분석보고서/LU_수태음폐경/LU06_공최/LU06_공최_해부생리_분석데이터.xlsx
+++ b/01_경혈별_해부생리_분석보고서/LU_수태음폐경/LU06_공최/LU06_공최_해부생리_분석데이터.xlsx
@@ -11,13 +11,15 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2.2대교재_해부구조_대조" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3.3D좌표_Layer1~5_심도" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4.생의학반사_BCheck_논문" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="구판_5.ARI_v3.0_평가표" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ARI_v3.0" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="B-Check" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LayerA_papers" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외부검색로그" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="개정이력" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FMA_해부실체" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="문헌스크리닝_4대원전_경락통감" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기추론_TriTarget" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="구판_5.ARI_v3.0_평가표" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ARI_v3.0" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="B-Check" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LayerA_papers" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외부검색로그" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="개정이력" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FMA_해부실체" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -53,7 +55,7 @@
       <color rgb="009C5700"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -69,6 +71,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DDEBF7"/>
       </patternFill>
     </fill>
   </fills>
@@ -98,7 +105,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -108,6 +115,12 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -621,248 +634,550 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>위치</t>
+          <t>papers.id</t>
         </is>
       </c>
       <c r="B1" s="3" t="inlineStr">
         <is>
-          <t>원래 내용</t>
+          <t>연도</t>
         </is>
       </c>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>바꾼 내용</t>
+          <t>저널</t>
         </is>
       </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
-          <t>근거</t>
+          <t>제목</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>저자</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>PMID</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>DOI</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>용도</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>md 1절</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>목차·타 혈위 OCR 파편</t>
-        </is>
+      <c r="A2" t="n">
+        <v>1682</v>
+      </c>
+      <c r="B2" t="n">
+        <v>2024</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>孔最 원문 발췌(《通考》·《穴位通鉴》·《证治通鉴》)</t>
+          <t>Zhongguo Zhen Jiu</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>《通考》(上)_81-160.md L2300–2467 등</t>
+          <t>Effect and mechanism of acupuncture on airway smooth muscle relaxation during acute asthma attack in rats.</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Qiao Y, Liang Y, Zhuo S, Yang X, Liang T, Ling X et al.</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>38467504</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>10.13703/j.0255-2930.20230426-k0004</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>T1 기전(동물, LU6+LU10)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>md 2·3·5·6·7·9절</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>자리표시자</t>
-        </is>
+      <c r="A3" t="n">
+        <v>1683</v>
+      </c>
+      <c r="B3" t="n">
+        <v>2023</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>원천/재인용 표, 이명 표(孔冣·泽田), 자침 깊이표, 교재 비교표, T1/T2 분기, 주치 분리</t>
+          <t>Zhongguo Zhen Jiu</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>자침깊이 xlsx 60행, 교재 xlsx 59행, KJH 61행</t>
+          <t>[Effects of acupuncture on pulmonary function and airway smooth muscle spasm in asthma rats].</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Shi YR, Yi W, Qiao Y, Zhuo SY, Zhang Q, Yang XJ et al.</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>37577892</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>10.13703/j.0255-2930.20220618-k0002</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>T1 기전(동물, LU6+LU10)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>md 8절 B-Check</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>9/12 확정</t>
-        </is>
+      <c r="A4" t="n">
+        <v>1684</v>
+      </c>
+      <c r="B4" t="n">
+        <v>2023</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>T1 7/12 미부합, T2 4/12 가설</t>
+          <t>Zhongguo Zhen Jiu</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>final_LU06.json</t>
+          <t>[Effect mechanism of acupuncture for anti-asthmatic airway remodeling based on TGF-β1 / Smad3 signaling pathway].</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Zhang Q, Qiao Y, Shi YR, Pang JL, Song SJ, Tang HY et al.</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>37313563</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>10.13703/j.0255-2930.20220412-k0013</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>T1 기전(동물, LU6+LU10)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>md 8절 Layer A</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>17·795·1458·1461·1002·1678 나열</t>
-        </is>
+      <c r="A5" t="n">
+        <v>1806</v>
+      </c>
+      <c r="B5" t="n">
+        <v>2025</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1682·1683·1684·1806·1726 중심, 讹传 논문 반증 분리</t>
+          <t>Korean Journal of Acupuncture</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>pack_LU6.md</t>
+          <t>Ultrasonographic Study on Forearm Acupuncture Points (LU6 and LI7) and Myotendinous Junction Relationships</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Yeon Kyeong Nam, S.H. Kim, Su bin Choi, Jae-Hyo Kim, O Sang Kwon</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>10.14406/acu.2025.024</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>T1 해부·영상(초음파)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>md 머리말</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>실측 논문 48편</t>
-        </is>
+      <c r="A6" t="n">
+        <v>1726</v>
+      </c>
+      <c r="B6" t="n">
+        <v>2012</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>근거 묶음 수치로 교체</t>
+          <t>中国中医急症</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>pack_LU6.md</t>
+          <t>针刺孔最穴鱼际穴治疗哮喘急性发作临床观察</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>李素荷</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>T1 인체 임상관찰(비RCT, LU6+LU10)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>md 10절</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>ARI-Core 79.0 B</t>
-        </is>
+      <c r="A7" t="n">
+        <v>1679</v>
+      </c>
+      <c r="B7" t="n">
+        <v>2009</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>T1 71.2 ± 0 B(가중치 민감) / T2 35 ± 0 D·H, T1 우위</t>
+          <t>J Altern Complement Med</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>final_LU06.json</t>
+          <t>Characteristics of electrical skin resistance at acupuncture points in healthy humans.</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Kramer S, Winterhalter K, Schober G, Becker U, Wiegele B, Kutz DF et al.</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>19422323</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>10.1089/acm.2008.0331</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>T1 보조(인체 피부저항)</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>구판 점수</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="A8" t="n">
+        <v>1807</v>
+      </c>
+      <c r="B8" t="n">
+        <v>2025</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>구판 v2.6 점수 79.0(비교 불가)</t>
+          <t>Annals of Medicine</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>_구판_v2.6/</t>
+          <t>Effect of press needle stimulation on postoperative pulmonary complications in video-assisted thoracoscopic surgery patients: a randomized controlled trial</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Jing Tan, Yong Dong Feng, Hui Liu, Yihu Zhou, Jiaqin Cai, Yueyi Jiang et al.</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>40953233</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>10.1080/07853890.2025.2560684</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>T1 보조(인체 RCT, 다혈)</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>xlsx 4.생의학반사_BCheck_논문</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>B3-11 (Longhurst), B3-16 (Torres-Rosas), papers.id #1 / PMID 확인</t>
-        </is>
+      <c r="A9" t="n">
+        <v>17</v>
+      </c>
+      <c r="B9" t="n">
+        <v>2002</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>구판 시트는 보존. 신규 B-Check 시트는 참조 ID만 표기. 등록부상 B3-11 = Zhao 2008 진통 종설, B3-16 = Liu 2020 NPY 교감 경로(Neuron)이며 B3-15가 Torres-Rosas 2014</t>
+          <t>Neuroscience Letters</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>layer_b_reference_registry.md L64·68·69</t>
+          <t>Unique Immunomodulation by Electro-acupuncture in Humans Possibly via Stimulation of the Autonomic Nervous System</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Mori H</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>B-Check ⑥ 참고만(다혈, LU6 특이성 미확인)</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>xlsx 시트</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>5.ARI_v3.0_평가표</t>
-        </is>
+      <c r="A10" t="n">
+        <v>1561</v>
+      </c>
+      <c r="B10" t="n">
+        <v>2011</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>구판_ 접두로 개명, ARI_v3.0·B-Check·LayerA_papers·외부검색로그·개정이력 추가</t>
+          <t>中医文献杂志</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>WRITER_BRIEF</t>
+          <t>“孔最治痔”讹传及其对当代针灸学的影响</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>黄幼民 黄龙祥</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>반증: 孔最治痔 讹传</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>FMA_해부실체 시트 신설 (2026-10-23)</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="A11" t="n">
+        <v>1563</v>
+      </c>
+      <c r="B11" t="n">
+        <v>2011</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>FMA 5.1.0 실체 ID·지배신경·줄기·분절·교재 비교 추가, '깊은엄지굽힘근'→긴엄지굽힘근 정정. T1 71.2 ± 0 (B)·T2 35 ± 0 (D·H) 불변</t>
+          <t>针刺研究</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>fma_query.py profile LU06; 보고서 4·6·8절·부록 A</t>
+          <t>“孔最治痔”的讹传及其对当代针灸学的影响</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>黄幼民 黄龙祥</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>반증: 孔最治痔 讹传</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1723</v>
+      </c>
+      <c r="B12" t="n">
+        <v>2011</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>针刺研究</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>孔最治痔的讹传及其对当代针灸学的影响</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>黄幼民</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>반증: 1563 별도 소장본</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>1564</v>
+      </c>
+      <c r="B13" t="n">
+        <v>2012</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>科学通报</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>从三个著名案例看针灸临床研究的复杂性</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>黄龙祥 黄幼民</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>10.1360/972011-743</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>반증: 비특이 효과 해석</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>461</v>
+      </c>
+      <c r="B14" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Korean Journal of Acupuncture</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>공최(LU6)를 활용한 치질치료의 근거에 대한 문헌고찰</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>조은별</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>10.14406/acu.2021.024</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>T2 문헌고찰</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>1742</v>
+      </c>
+      <c r="B15" t="n">
+        <v>2018</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>World Journal of Acupuncture-Moxibustion</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Acupuncture at Kongzui (LU6) for 76 cases of hemorrhoids</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Li XY</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>T2 증례군</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>1808</v>
+      </c>
+      <c r="B16" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Journal of Agromedicine and Medical Sciences</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>The Effectiveness of Acupuncture Therapy in Patient with Hemorrhoid: A Case Report</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Fieka Meitaqwatiningarum, Christina Lanny Simadibrata, Irma Nareswari</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>10.19184/ams.v7i3.23937</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>T2 증례보고</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>제외</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>17·795·1458·1461·1002·1678은 구판에서 실증 근거로 나열됐으나 LU6 기전 근거가 아니어서 제외(17은 참고 표기만)</t>
         </is>
       </c>
     </row>
@@ -872,6 +1187,572 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>일시</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>소스</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>수집</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>중복제거</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>쿼리</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-10-04T09:51:32</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>pubmed</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>200</v>
+      </c>
+      <c r="D2" t="n">
+        <v>9</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>("LU6" OR "Kongzui" OR "孔最") AND (acupuncture OR electroacupuncture) AND (nerve OR reflex OR autonomic OR mechanism OR anatomy)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-10-04T09:51:32</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>openalex</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>200</v>
+      </c>
+      <c r="D3" t="n">
+        <v>16</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>doi_starts_with:10.13703,title_and_abstract.search:"Kongzui" OR "LU6" | doi_starts_with:10.13702,… | has_doi:true,…</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-10-04T09:51:32</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>crossref</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>200</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Kongzui acupuncture nerve reflex</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-10-04T09:51:32</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>25</v>
+      </c>
+      <c r="E5" t="n">
+        <v>25</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-10-23T21:44:38</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>pubmed</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>200</v>
+      </c>
+      <c r="D6" t="n">
+        <v>9</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>("LU6" OR "Kongzui" OR "孔最") AND (acupuncture OR electroacupuncture) AND (nerve OR reflex OR autonomic OR mechanism OR anatomy) | ("LU6" OR "Kongzui" OR "孔最") AND ("Zhongguo Zhen Jiu"[Journal] OR "Zhen Ci Yan Jiu"[Journal])</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-10-23T21:44:38</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>openalex</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>200</v>
+      </c>
+      <c r="D7" t="n">
+        <v>16</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>doi_starts_with:10.13703,title_and_abstract.search:"Kongzui" OR "LU6" | doi_starts_with:10.13702,title_and_abstract.search:"Kongzui" OR "LU6" | has_doi:true,title_and_abstract.search:"Kongzui" OR "LU6" AND (acupuncture OR electroacupuncture)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-10-23T21:44:38</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>crossref</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>200</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Kongzui acupuncture nerve reflex</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-10-23T21:44:38</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>25</v>
+      </c>
+      <c r="E9" t="n">
+        <v>25</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>위치</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>원래 내용</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>바꾼 내용</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>근거</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>md 1절</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>목차·타 혈위 OCR 파편</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>孔最 원문 발췌(《通考》·《穴位通鉴》·《证治通鉴》)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>《通考》(上)_81-160.md L2300–2467 등</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>md 2·3·5·6·7·9절</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>자리표시자</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>원천/재인용 표, 이명 표(孔冣·泽田), 자침 깊이표, 교재 비교표, T1/T2 분기, 주치 분리</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>자침깊이 xlsx 60행, 교재 xlsx 59행, KJH 61행</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>md 8절 B-Check</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>9/12 확정</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>T1 7/12 미부합, T2 4/12 가설</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>final_LU06.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>md 8절 Layer A</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>17·795·1458·1461·1002·1678 나열</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1682·1683·1684·1806·1726 중심, 讹传 논문 반증 분리</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>pack_LU6.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>md 머리말</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>실측 논문 48편</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>근거 묶음 수치로 교체</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>pack_LU6.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>md 10절</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ARI-Core 79.0 B</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>T1 71.2 ± 0 B(가중치 민감) / T2 35 ± 0 D·H, T1 우위</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>final_LU06.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>구판 점수</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>구판 v2.6 점수 79.0(비교 불가)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>_구판_v2.6/</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>xlsx 4.생의학반사_BCheck_논문</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>B3-11 (Longhurst), B3-16 (Torres-Rosas), papers.id #1 / PMID 확인</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>구판 시트는 보존. 신규 B-Check 시트는 참조 ID만 표기. 등록부상 B3-11 = Zhao 2008 진통 종설, B3-16 = Liu 2020 NPY 교감 경로(Neuron)이며 B3-15가 Torres-Rosas 2014</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>layer_b_reference_registry.md L64·68·69</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>xlsx 시트</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>5.ARI_v3.0_평가표</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>구판_ 접두로 개명, ARI_v3.0·B-Check·LayerA_papers·외부검색로그·개정이력 추가</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>WRITER_BRIEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>FMA_해부실체 시트 신설 (2026-10-23)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>FMA 5.1.0 실체 ID·지배신경·줄기·분절·교재 비교 추가, '깊은엄지굽힘근'→긴엄지굽힘근 정정. T1 71.2 ± 0 (B)·T2 35 ± 0 (D·H) 불변</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>fma_query.py profile LU06; 보고서 4·6·8절·부록 A</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-25 Framework 2.7.7 (md 머리말·1·2·3·4·5·7·8·9·10절, xlsx)</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>3대 원전, T1 표준/T2 泽田 Dual-Target(Δ &gt; 15mm), ④ 通考 교감</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>4대 원전(经络通鉴 행·Rank 4 교감), 证治通鉴 한글 번역본 병기, 자입 기준점(위팔노근 내측연 간극), Tri-Target 10mm 기준 Target 1≡2≡3(쌍별 ≈0~6mm 추정) + 泽田 동명이위혈 분기, ④ 재확인 불변, ARI 불변(71.2 ± 0 B / 35 ± 0 D·H); 시트 문헌스크리닝_4대원전_경락통감·분기추론_TriTarget 신설, ARI_v3.0 Target 라벨 변경</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>프레임워크 2.7.7; 분기 기준 Δ &gt; 10mm(2026-10-25 개정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-25 Target 제외 규칙 (md 머리말·2·3·4·5·7·8·9·10절, xlsx)</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>泽田 공최 = 동명이위혈 분기, 이중 채점 35 ± 0 D·H·SI 50·B-Check 4/12, ΔARI 36.2 분기 판정</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>泽田 공최를 Target에서 제외(근현대 신설 혈): 4절 정위 주석·7-2 참고 이설로만 기록, B-Check 표·10-2 채점표·10-3 분기 판정 삭제, 구 채점은 "2026-10-04 채점 기록 — 판정 철회" 메모로만 보존; 10寸 과도기 변이도 제외 규칙 사유 명시; 표준 공최 71.2 ± 0 B·SI 75 불변; ARI_v3.0·B-Check 시트 泽田 행 라벨 "참고(Target 제외)", 분기추론_TriTarget 판정 갱신</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>프레임워크 Rank 5 Target 제외 규칙(2026-10-25)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -988,7 +1869,6 @@
           <t>C6(primary/segmental), C5(secondary/segmental)</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1034,7 +1914,6 @@
           <t>C6(primary/segmental), C7(secondary/segmental)</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1130,7 +2009,6 @@
           <t>C8(primary/segmental), T1(secondary/segmental)</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1226,7 +2104,6 @@
           <t>C7(segmental), C8(segmental)</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1272,7 +2149,6 @@
           <t>C7(primary/segmental), C6(secondary/segmental)</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1303,7 +2179,6 @@
           <t>공통교재·김재효</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
           <t>FMA:288511 Peripheral segment of musculocutaneous nerve</t>
@@ -1314,7 +2189,6 @@
           <t>FMA 미기재</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1345,7 +2219,6 @@
           <t>공통교재·김재효</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
           <t>FMA:37069 Radial nerve</t>
@@ -1356,7 +2229,6 @@
           <t>FMA 미기재</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1387,7 +2259,6 @@
           <t>공통교재·김재효</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
           <t>FMA:13324 Cephalic vein → FMA:4725 Subclavian vein → FMA:4723 Brachiocephalic vein</t>
@@ -1398,7 +2269,6 @@
           <t>FMA 미기재</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1429,7 +2299,6 @@
           <t>공통교재·김재효</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
           <t>FMA:4725 Subclavian vein → FMA:4723 Brachiocephalic vein</t>
@@ -1440,7 +2309,6 @@
           <t>FMA 미기재</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1471,7 +2339,6 @@
           <t>공통교재·김재효</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
           <t>FMA:3951 Subclavian artery</t>
@@ -1517,7 +2384,6 @@
           <t>공통교재·김재효</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
           <t>FMA:22934 Brachial vein → FMA:13329 Axillary vein → FMA:4725 Subclavian vein → FMA:4723 Brachiocephalic vein</t>
@@ -1528,7 +2394,6 @@
           <t>FMA 미기재</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2136,209 +3001,283 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="70" customWidth="1" min="5" max="5"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>⚠ 구판 v2.6 데이터 시트 — 원전 대조·채점 오류가 포함되어 있을 수 있음. 2026-10-04 v2.7 개정본 .md 보고서와 'ARI_v3.0'·'B-Check'·'개정이력' 시트가 정본.</t>
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>원전</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>원문 발췌</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>한국어 요지</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>판정 용도</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>내부 포인터(파일·행)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>구분</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>지표명</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t>가중치</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t>원점수 (0~100)</t>
-        </is>
-      </c>
-      <c r="E2" s="1" t="inlineStr">
-        <is>
-          <t>가중점수</t>
-        </is>
-      </c>
-      <c r="F2" s="1" t="inlineStr">
-        <is>
-          <t>루브릭 단계 및 판정 근거</t>
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>《中国针灸经络通鉴》</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>《甲乙》 "孔最，手太阴之郄，去腕七寸，专（此处缺文）金二七，水之父母，刺入三分，留三呼，灸五壮"</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>去腕七寸·3분 확인, "专…金二七" 결문(전사 손상, 미교정)</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>Target 1 근거, Rank 4</t>
+        </is>
+      </c>
+      <c r="E2" s="6" t="inlineStr">
+        <is>
+          <t>中国针灸经络通鉴_11_第贰编_第三篇_脉度、骨度与要穴.md L683</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>ARI-Core</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>S_orig (원전문헌 정합성)</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="D3" s="2" t="n">
-        <v>85</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>34</v>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>선진·한대 원천정위 및 3대 원전 편년체 전수 대조</t>
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>《中国针灸经络通鉴》</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>《灵枢·寒热病》 "病始手臂者，先取手阳明、太阴而汗出" / 《太素》 杨注 "手太阴郄孔最，在腕上七寸也" / 【按】 "《明堂》谓孔最穴可以出汗"</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>汗 주치가 杨注를 거쳐 《灵枢》 取穴과 연결(보조 근거)</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>P_single 汗不出, Rank 3</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>中国针灸经络通鉴_18_第叁编_第二篇_手阳明经脉、经别、络脉和经筋.md L896~904</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>ARI-Core</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>S_clarity (해부 실체 명확성)</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>75</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>26.25</v>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>공통교재 vs 김재효 교재 정밀 비교 및 3D 층차 실체화</t>
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>《中国针灸经络通鉴》</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>《医学纲目》 주 "臂有二骨，今太阴脉循臂上骨之下廉也" / 《经络汇编》 "循臂内上骨之下廉，历孔最、列缺"</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>경맥 순행 = 노뼈 자쪽 가장자리</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>Target 1 X 근거</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>中国针灸经络通鉴_17_第叁编_第一篇_手太阴经脉、经别、络脉和经筋.md L241·L281</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>ARI-Core</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>S_reflex (신경반사 실증성)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="D5" s="2" t="n">
-        <v>75</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>18.75</v>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>통합 DB 실측 논문 48편 + B-Check 9/12 부합</t>
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>《中国针灸经络通鉴》</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>《甲乙》·《明堂》 수태음 혈 목록(孔最 포함), 明堂 시대 肘膝以下 혈만 归经 해설</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>孔最 郄穴 归经 확인</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>2절 참고</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>中国针灸经络通鉴_17_第叁编_第一篇_手太阴经脉、经别、络脉和经筋.md L390·L400·L415</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>ARI-Core 총합</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>실체 판명 신뢰도</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>79</v>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>최종 등급: B (개연 (Probable))</t>
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>《中国针灸经络通鉴》</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>《甲乙经》 편명 "足太阳脉动发下部痔脱肛"</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>痔 = 足太阳 脉动 병후. 孔最 치질·泽田 공최 직접 언급 없음</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>Rank 4 주치 전이(간접)</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>中国针灸经络通鉴_17_第叁编_第一篇_手太阴经脉、经别、络脉和经筋.md L669; 전 39편 grep 孔最·孔冣·泽田·澤田·针灸真髓 — 그 외 관련 기술 없음</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>SI (안전지수)</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>S_safety (자침 심도 안전성)</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>별도</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="n">
-        <v>75</v>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>75</v>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>한대 1푼=2.3mm 환산 및 Layer 4~5 안전 여유 거리</t>
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>《中国针灸证治通鉴》</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>"伤寒热病身无汗，细详孔最患无妨。"(玉龙歌)</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>(번역본) 상한·열병에 땀이 없으면 공최를 자세히 살펴 쓰면 병이 걱정 없다</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>P_comb/참고</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>中国针灸证治通鉴_15_第叁编_内科病症_九厥证至十五疠风.md L752; 中国针灸证治通鉴_15_第叁编_内科病症_九厥证至十五疠风_한글번역.md L1215·L1217</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>민감도 분석</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>등가중치(1/3씩) ARI-Core</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>78.33</v>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>민감도 판정: B (등급 불변)</t>
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>《中国针灸证治通鉴》</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>"热病烦心，汗不出：中冲、劳宫……孔最三壮至五壮，即汗。"(针灸捷径)</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>(번역본) 열병 번심 무한: …공최에 3~5장 뜨면 곧 땀이 난다. 번역본 인용 원문 "劳官" 오자</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>P_comb</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>中国针灸证治通鉴_15_第叁编_内科病症_九厥证至十五疠风.md L796; 中国针灸证治通鉴_15_第叁编_内科病症_九厥证至十五疠风_한글번역.md L1289·L1291</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>《中国针灸证治通鉴》</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>咯血 "孔最配尺泽。强刺激为主。" / 哮喘 "孔最、鱼际。"</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>(번역본) 공최에 척택 배합, 강자극 위주 / 공최·어제</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>P_comb</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>中国针灸证治通鉴_17_第叁编_内科病症_二十二脏腑病证至二十四胸胁满痛.md L1413·L1263; 中国针灸证治通鉴_17_第叁编_内科病症_二十二脏腑病证至二十四胸胁满痛_한글번역.md L2260·L2048</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>《中国针灸证治通鉴》</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>转筋汗不出 / 烦心汗不出 / 咳嗽汗不出 … 孔最三壮</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>(번역본) 전근·번심·해수에 땀이 나지 않을 때 공최 뜸 3장</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>P_comb(汗 계열)</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>中国针灸证治通鉴_18_第叁编_内科病症_二十五劳瘵至三十消渴.md L540·L542·L552; 中国针灸证治通鉴_18_第叁编_内科病症_二十五劳瘵至三十消渴_한글번역.md L898·L902·L922</t>
         </is>
       </c>
     </row>
@@ -2353,458 +3292,362 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R12"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="52" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>Target</t>
-        </is>
-      </c>
-      <c r="B1" s="3" t="inlineStr">
-        <is>
-          <t>라벨</t>
-        </is>
-      </c>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>지표</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>채점자 A</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>채점자 B</t>
-        </is>
-      </c>
-      <c r="F1" s="3" t="inlineStr">
-        <is>
-          <t>평균</t>
-        </is>
-      </c>
-      <c r="G1" s="3" t="inlineStr">
-        <is>
-          <t>S_orig 하위(A)</t>
-        </is>
-      </c>
-      <c r="H1" s="3" t="inlineStr">
-        <is>
-          <t>S_orig 하위(B)</t>
-        </is>
-      </c>
-      <c r="I1" s="3" t="inlineStr">
-        <is>
-          <t>게이트</t>
-        </is>
-      </c>
-      <c r="J1" s="3" t="inlineStr">
-        <is>
-          <t>ARI-Core</t>
-        </is>
-      </c>
-      <c r="K1" s="3" t="inlineStr">
-        <is>
-          <t>± 반범위</t>
-        </is>
-      </c>
-      <c r="L1" s="3" t="inlineStr">
-        <is>
-          <t>등급</t>
-        </is>
-      </c>
-      <c r="M1" s="3" t="inlineStr">
-        <is>
-          <t>표지</t>
-        </is>
-      </c>
-      <c r="N1" s="3" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="O1" s="3" t="inlineStr">
-        <is>
-          <t>등가중치 Core</t>
-        </is>
-      </c>
-      <c r="P1" s="3" t="inlineStr">
-        <is>
-          <t>등가중치 등급</t>
-        </is>
-      </c>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>가중치 민감</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="inlineStr">
-        <is>
-          <t>표기</t>
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>Target 1 (고전 문헌 위치)</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>Target 2 (촉진 실체화·자입 기준점)</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>Target 3 (WHO 위치)</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>비고</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>WHO·교재 표준 공최(腕上七寸, 尺泽–太渊 연선, 《黄帝明堂经》 정위)</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>S_orig</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>81.25</v>
-      </c>
-      <c r="E2" t="n">
-        <v>81.25</v>
-      </c>
-      <c r="F2" t="n">
-        <v>81.25</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>100/75/75/75</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>75/75/75/100</t>
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>근거</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>《明堂》·《甲乙》 "去腕七寸"; 순행 "循臂内上骨下廉"</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>元 《玉龙经》 "宛宛中", 清 《医宗金鉴》 "上骨下，骨间陷中", 《新针灸学》 "肱桡肌之内缘…屈拇长肌之外缘"</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>WHO 2008 尺泽–太渊 연선 腕上七寸</t>
+        </is>
+      </c>
+      <c r="E2" s="6" t="inlineStr">
+        <is>
+          <t>经络通鉴 11편 L683, 17편 L241; 通考 L2320</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>WHO·교재 표준 공최(腕上七寸, 尺泽–太渊 연선, 《黄帝明堂经》 정위)</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>S_clarity</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>75</v>
-      </c>
-      <c r="E3" t="n">
-        <v>75</v>
-      </c>
-      <c r="F3" t="n">
-        <v>75</v>
-      </c>
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>노뼈 자쪽 가장자리 위</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>위팔노근(FMA:38485) 내측연–노쪽손목굽힘근(FMA:38459)·원엎침근 정지부(FMA:38450) 간극, 바닥 긴엄지굽힘근(FMA:38481)</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>尺泽–太渊 연선(위팔노근 내측연)</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>WHO·교재 표준 공최(腕上七寸, 尺泽–太渊 연선, 《黄帝明堂经》 정위)</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>S_reflex</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>50</v>
-      </c>
-      <c r="E4" t="n">
-        <v>50</v>
-      </c>
-      <c r="F4" t="n">
-        <v>50</v>
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Y (전완 250mm 가정)</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>≈ 140mm (12.5寸 골도)</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>≈ 140mm (腕上七寸 전제)</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>≈ 146mm (12寸 골도)</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>추정</t>
+        </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>WHO·교재 표준 공최(腕上七寸, 尺泽–太渊 연선, 《黄帝明堂经》 정위)</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>S_safety</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>75</v>
-      </c>
-      <c r="E5" t="n">
-        <v>75</v>
-      </c>
-      <c r="F5" t="n">
-        <v>75</v>
-      </c>
+      <c r="A5" s="6" t="n"/>
+      <c r="B5" s="6" t="n"/>
+      <c r="C5" s="6" t="n"/>
+      <c r="D5" s="6" t="n"/>
+      <c r="E5" s="6" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>WHO·교재 표준 공최(腕上七寸, 尺泽–太渊 연선, 《黄帝明堂经》 정위)</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>종합</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>없음</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
-        <v>71.2</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="N6" t="n">
-        <v>75</v>
-      </c>
-      <c r="O6" t="n">
-        <v>68.8</v>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>예</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>ARI v3.0 | ARI-Core 71.2 ± 0 (B) | SI 75 | 잠정 가중치 0.40/0.35/0.25 | 민감도(등가중치): 68.8 (C, 등급 변동 → 가중치 민감)</t>
-        </is>
-      </c>
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>쌍</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>Δ (추정)</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>근거</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>판정 (10mm 기준)</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>T2</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>사와다(泽田)식 공최 치질 반응점(《针灸真髓》 1941, 尺泽下二寸)</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>S_orig</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>50</v>
-      </c>
-      <c r="E7" t="n">
-        <v>50</v>
-      </c>
-      <c r="F7" t="n">
-        <v>50</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>25/25/75/75</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>25/25/75/75</t>
-        </is>
-      </c>
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>T1–T2</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>≈ 0~5mm</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>같은 높이, X만 수 mm</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>병합</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>T2</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>사와다(泽田)식 공최 치질 반응점(《针灸真髓》 1941, 尺泽下二寸)</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>S_clarity</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>25</v>
-      </c>
-      <c r="E8" t="n">
-        <v>25</v>
-      </c>
-      <c r="F8" t="n">
-        <v>25</v>
-      </c>
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>T1–T3</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>≈ 6mm</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>7×250/12.5=140 vs 7×250/12≈146</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>병합</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>T2</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>사와다(泽田)식 공최 치질 반응점(《针灸真髓》 1941, 尺泽下二寸)</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>S_reflex</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>25</v>
-      </c>
-      <c r="E9" t="n">
-        <v>25</v>
-      </c>
-      <c r="F9" t="n">
-        <v>25</v>
-      </c>
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>T2–T3</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>≈ 6mm</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>같은 골도 차이</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>병합</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>T2</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>사와다(泽田)식 공최 치질 반응점(《针灸真髓》 1941, 尺泽下二寸)</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>S_safety</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>50</v>
-      </c>
-      <c r="E10" t="n">
-        <v>50</v>
-      </c>
-      <c r="F10" t="n">
-        <v>50</v>
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>결론</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>Target 1≡2≡3 (단일 표준 공최)</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr"/>
+      <c r="D10" s="6" t="inlineStr"/>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>구 T1과 위치 동일 → 이중 채점 승계(71.2 ± 0 B)</t>
+        </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>T2</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>사와다(泽田)식 공최 치질 반응점(《针灸真髓》 1941, 尺泽下二寸)</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>종합</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>게이트1(S_orig 또는 S_clarity &lt; 50 → 최고 C); 게이트2(경혈 특이 Layer A 0편 → S_reflex ≤ 25, H)</t>
-        </is>
-      </c>
-      <c r="J11" t="n">
-        <v>35</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>D·H</t>
-        </is>
-      </c>
-      <c r="N11" t="n">
-        <v>50</v>
-      </c>
-      <c r="O11" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>아니오</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>ARI v3.0 | ARI-Core 35 ± 0 (D·H) | SI 50 | 잠정 가중치 0.40/0.35/0.25 | 민감도(등가중치): 33.3 (D, 등급 불변)</t>
-        </is>
-      </c>
+      <c r="A11" s="6" t="n"/>
+      <c r="B11" s="6" t="n"/>
+      <c r="C11" s="6" t="n"/>
+      <c r="D11" s="6" t="n"/>
+      <c r="E11" s="6" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>분기</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>ΔARI-Core = 71.2 − 35 = 36.2 (≥10), 구간 비중첩 → T1 우위</t>
-        </is>
-      </c>
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Tri-Target 밖</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>Δ (추정)</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>근거</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>처리 (Rank 5 Target 제외 규칙)</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>10寸 골도 과도기 腕上七寸</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>≈ 175mm; Target 3과 ≈ 29mm, Target 1과 ≈ 35mm</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>골도 환산 과도기 위치(표 4-1)</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>Target 제외(환산 척도 이문) — 4절·7절 참고 변이로만 기록</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>泽田 공최 (근현대 신설 혈)</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>Target 1≡2≡3과 ≈ 42~62mm</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>尺泽下 3횡지 반응점(1941 창안)</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>Target 제외(근현대 신설 혈) — 분기·채점 없음, 7-2 참고 이설</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>구 채점 35 ± 0 D·H는 2026-10-04 기록으로만 보존, 판정 철회</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>판정</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>단일 Target</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr"/>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>표준 공최 Target 1≡2≡3 (71.2 ± 0 B)</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>분기·우위 판정 없음(구 ΔARI 36.2 철회)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="n"/>
+      <c r="B16" s="6" t="n"/>
+      <c r="C16" s="6" t="n"/>
+      <c r="D16" s="6" t="n"/>
+      <c r="E16" s="6" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>구판 대응</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>구 T1 → Target 1≡2≡3; 구 T2 → 참고 이설(Target 제외)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr"/>
+      <c r="D17" s="6" t="inlineStr"/>
+      <c r="E17" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2817,538 +3660,209 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>Target</t>
-        </is>
-      </c>
-      <c r="B1" s="3" t="inlineStr">
-        <is>
-          <t>항목</t>
-        </is>
-      </c>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>채점자 A</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>채점자 B</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>최종</t>
-        </is>
-      </c>
-      <c r="F1" s="3" t="inlineStr">
-        <is>
-          <t>Layer B 참조 ID</t>
-        </is>
-      </c>
-      <c r="G1" s="3" t="inlineStr">
-        <is>
-          <t>papers.id</t>
-        </is>
-      </c>
-      <c r="H1" s="3" t="inlineStr">
-        <is>
-          <t>근거 요지(A)</t>
-        </is>
-      </c>
-      <c r="I1" s="3" t="inlineStr">
-        <is>
-          <t>근거 요지(B)</t>
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>⚠ 구판 v2.6 데이터 시트 — 원전 대조·채점 오류가 포함되어 있을 수 있음. 2026-10-04 v2.7 개정본 .md 보고서와 'ARI_v3.0'·'B-Check'·'개정이력' 시트가 정본.</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>지표명</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>가중치</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>원점수 (0~100)</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>가중점수</t>
+        </is>
+      </c>
+      <c r="F2" s="1" t="inlineStr">
+        <is>
+          <t>루브릭 단계 및 판정 근거</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>ARI-Core</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>S_orig (원전문헌 정합성)</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>선진·한대 원천정위 및 3대 원전 편년체 전수 대조</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>ARI-Core</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>S_clarity (해부 실체 명확성)</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>26.25</v>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>공통교재 vs 김재효 교재 정밀 비교 및 3D 층차 실체화</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>ARI-Core</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>S_reflex (신경반사 실증성)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>통합 DB 실측 논문 48편 + B-Check 9/12 부합</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>ARI-Core 총합</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>실체 판명 신뢰도</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C2" t="n">
-        <v>2</v>
-      </c>
-      <c r="D2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E2" t="n">
-        <v>2</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>B1-01, B1-03, B2-02, B2-09, B2-10</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>1806</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>2대 교재 모두 가쪽아래팔피부신경·노신경 얕은가지·노동정맥·노쪽피부정맥을 명시하고, 혈위 특이 초음파 실측(1806)이 있음</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2대 교재 구조 일치 + LU6 특이 초음파 실측(1806)으로 자침층 실체 확인</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>B1-02, B1-03, B3-01, B3-20</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>피절 C5–C6(가쪽아래팔피부신경)은 폐의 교감 내장절(T1–T5)과 직접 맞지 않아 간접·유추 수준</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>피절 C5–C7(가쪽아래팔피부신경·노신경) vs 폐 내장절 T1–T5·미주 — 직접 분절 정합 아님, 유추 수준. 보고서의 2점은 근거 없음</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>3</v>
-      </c>
-      <c r="C4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>B3-05, B3-06</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>1682</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>구심 섬유형은 일반 동물 기전에서 유추한 것이며 LU6 특이 구심 섬유 연구는 없음. B3-17(ST36 PROKR2)은 범위 밖</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>LU6 구심 섬유형·수용체 실측 없음, 일반 체계 유추</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>4</v>
-      </c>
-      <c r="C5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>B3-04, B3-05</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>체성-자율 반사의 상척수 경로를 유추. LU6에서 NTS·미주 경로를 확인한 연구 없음</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>중추 경로(NTS 등) LU6 특이 근거 없음, 유추</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>5</v>
-      </c>
-      <c r="C6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>B3-05</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>1682, 1683, 1684</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>천식 쥐에서 기도평활근 이완(β2-AR, ET-1)으로 고전 주치 '咳逆'(동인)과 방향이 같으나, 동물·짝혈 연구임. 《明堂》 원주치 '汗不出'(발한)에 대한 원심 기전 근거는 없음</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>쥐 천식 모델에서 기도평활근 이완(咳逆·气喘 방향 일치)이나 동물·LU10 배합 한정. 명당경 단독 주치(热病汗不出)와의 기전 연결은 없음. 보고서의 2점은 과대</t>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>79</v>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>최종 등급: B (개연 (Probable))</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>6</v>
-      </c>
-      <c r="C7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>B4-03, B4-04, B4-05</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>17, 1679, 1726, 1807</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>인체 연구는 다혈 조합에서만 있고 LU6 단독 효과는 분리되지 않음</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>비RCT 임상관찰·피부저항 측정 수준, 혈위 특이성 반증(B4-05) 병기 필요</t>
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>SI (안전지수)</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>S_safety (자침 심도 안전성)</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>별도</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>한대 1푼=2.3mm 환산 및 Layer 4~5 안전 여유 거리</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>합계</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>7</v>
-      </c>
-      <c r="D8" t="n">
-        <v>7</v>
-      </c>
-      <c r="E8" t="n">
-        <v>7</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>판정: 미부합</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>T2</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>B1-01, B1-03</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>규범 해부로 위팔노근·노신경 분지 부위를 추정할 뿐이며 교재와 실측 근거가 없음</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>교재·실측 없음, 규범 해부서 유추만</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>T2</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>2</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>B1-03, B3-01</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>C5–C6 피절과 항문직장(S2–S4, T10–L2 자율 분절) 사이에 분절 대응이 없음. 사와다의 '肺络于大肠' 경락 논리만 있음</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>피절 C5–C7 vs 항문·직장 S2–S4(하부 T10–L2 교감) — 분절 정합 부재. 泽田의 '肺络大肠' 경락 논리 외 근거 없음</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>T2</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>3</v>
-      </c>
-      <c r="C11" t="n">
-        <v>1</v>
-      </c>
-      <c r="D11" t="n">
-        <v>1</v>
-      </c>
-      <c r="E11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>B3-06</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>일반 구심 섬유형에서 유추한 것뿐임</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>일반 구심 섬유 유추</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>T2</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>4</v>
-      </c>
-      <c r="C12" t="n">
-        <v>1</v>
-      </c>
-      <c r="D12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E12" t="n">
-        <v>1</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>B3-07, B3-08</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>강자극에 의한 DNIC·관문조절 같은 비특이 진통 경로로만 설명 가능</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>강자극 비특이 진통(DNIC)으로 유추 가능, 혈위 특이 경로 아님</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>T2</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>5</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>B3-05, B4-05</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>치핵 혈류나 항문괄약근으로 가는 원심 경로 근거가 없음. 《通考》는 비특이 효과라고 반론함</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>고전 단독 주치에 치질 없음(《通考》), 원심 효과 방향 근거 부재</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>T2</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>6</v>
-      </c>
-      <c r="C14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D14" t="n">
-        <v>1</v>
-      </c>
-      <c r="E14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>B4-04, B4-05</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>1742, 1808</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>인체 증례와 증례군 보고만 있고 대조군이 없으며 취혈 위치가 불명확함</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>증례군·증례보고 수준, 비특이성 반증(B4-05, papers.id 1564) 병존</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>T2</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>합계</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>4</v>
-      </c>
-      <c r="D15" t="n">
-        <v>4</v>
-      </c>
-      <c r="E15" t="n">
-        <v>4</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>판정: 가설</t>
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>민감도 분석</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>등가중치(1/3씩) ARI-Core</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>78.33</v>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>민감도 판정: B (등급 불변)</t>
         </is>
       </c>
     </row>
@@ -3363,550 +3877,456 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:R12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>papers.id</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="B1" s="3" t="inlineStr">
         <is>
-          <t>연도</t>
+          <t>라벨</t>
         </is>
       </c>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>저널</t>
+          <t>지표</t>
         </is>
       </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
-          <t>제목</t>
+          <t>채점자 A</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>저자</t>
+          <t>채점자 B</t>
         </is>
       </c>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>PMID</t>
+          <t>평균</t>
         </is>
       </c>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>DOI</t>
+          <t>S_orig 하위(A)</t>
         </is>
       </c>
       <c r="H1" s="3" t="inlineStr">
         <is>
-          <t>용도</t>
+          <t>S_orig 하위(B)</t>
+        </is>
+      </c>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>게이트</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="inlineStr">
+        <is>
+          <t>ARI-Core</t>
+        </is>
+      </c>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>± 반범위</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="inlineStr">
+        <is>
+          <t>등급</t>
+        </is>
+      </c>
+      <c r="M1" s="3" t="inlineStr">
+        <is>
+          <t>표지</t>
+        </is>
+      </c>
+      <c r="N1" s="3" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="O1" s="3" t="inlineStr">
+        <is>
+          <t>등가중치 Core</t>
+        </is>
+      </c>
+      <c r="P1" s="3" t="inlineStr">
+        <is>
+          <t>등가중치 등급</t>
+        </is>
+      </c>
+      <c r="Q1" s="3" t="inlineStr">
+        <is>
+          <t>가중치 민감</t>
+        </is>
+      </c>
+      <c r="R1" s="3" t="inlineStr">
+        <is>
+          <t>표기</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>1682</v>
-      </c>
-      <c r="B2" t="n">
-        <v>2024</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>T1≡2≡3</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>표준 공최 Target 1≡2≡3 (고전 去腕七寸 ≡ 위팔노근 내측연 자입 기준점 ≡ WHO 腕上七寸)</t>
+        </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Zhongguo Zhen Jiu</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Effect and mechanism of acupuncture on airway smooth muscle relaxation during acute asthma attack in rats.</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Qiao Y, Liang Y, Zhuo S, Yang X, Liang T, Ling X et al.</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>38467504</t>
-        </is>
+          <t>S_orig</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>81.25</v>
+      </c>
+      <c r="E2" t="n">
+        <v>81.25</v>
+      </c>
+      <c r="F2" t="n">
+        <v>81.25</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>10.13703/j.0255-2930.20230426-k0004</t>
+          <t>100/75/75/75</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>T1 기전(동물, LU6+LU10)</t>
+          <t>75/75/75/100</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>1683</v>
-      </c>
-      <c r="B3" t="n">
-        <v>2023</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>T1≡2≡3</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>표준 공최 Target 1≡2≡3 (고전 去腕七寸 ≡ 위팔노근 내측연 자입 기준점 ≡ WHO 腕上七寸)</t>
+        </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Zhongguo Zhen Jiu</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>[Effects of acupuncture on pulmonary function and airway smooth muscle spasm in asthma rats].</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Shi YR, Yi W, Qiao Y, Zhuo SY, Zhang Q, Yang XJ et al.</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>37577892</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>10.13703/j.0255-2930.20220618-k0002</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>T1 기전(동물, LU6+LU10)</t>
-        </is>
+          <t>S_clarity</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>75</v>
+      </c>
+      <c r="E3" t="n">
+        <v>75</v>
+      </c>
+      <c r="F3" t="n">
+        <v>75</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
-        <v>1684</v>
-      </c>
-      <c r="B4" t="n">
-        <v>2023</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>T1≡2≡3</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>표준 공최 Target 1≡2≡3 (고전 去腕七寸 ≡ 위팔노근 내측연 자입 기준점 ≡ WHO 腕上七寸)</t>
+        </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Zhongguo Zhen Jiu</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>[Effect mechanism of acupuncture for anti-asthmatic airway remodeling based on TGF-β1 / Smad3 signaling pathway].</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Zhang Q, Qiao Y, Shi YR, Pang JL, Song SJ, Tang HY et al.</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>37313563</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>10.13703/j.0255-2930.20220412-k0013</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>T1 기전(동물, LU6+LU10)</t>
-        </is>
+          <t>S_reflex</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>50</v>
+      </c>
+      <c r="E4" t="n">
+        <v>50</v>
+      </c>
+      <c r="F4" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
-        <v>1806</v>
-      </c>
-      <c r="B5" t="n">
-        <v>2025</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>T1≡2≡3</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>표준 공최 Target 1≡2≡3 (고전 去腕七寸 ≡ 위팔노근 내측연 자입 기준점 ≡ WHO 腕上七寸)</t>
+        </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Korean Journal of Acupuncture</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Ultrasonographic Study on Forearm Acupuncture Points (LU6 and LI7) and Myotendinous Junction Relationships</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Yeon Kyeong Nam, S.H. Kim, Su bin Choi, Jae-Hyo Kim, O Sang Kwon</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>10.14406/acu.2025.024</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>T1 해부·영상(초음파)</t>
-        </is>
+          <t>S_safety</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>75</v>
+      </c>
+      <c r="E5" t="n">
+        <v>75</v>
+      </c>
+      <c r="F5" t="n">
+        <v>75</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
-        <v>1726</v>
-      </c>
-      <c r="B6" t="n">
-        <v>2012</v>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>T1≡2≡3</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>표준 공최 Target 1≡2≡3 (고전 去腕七寸 ≡ 위팔노근 내측연 자입 기준점 ≡ WHO 腕上七寸)</t>
+        </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>中国中医急症</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>针刺孔最穴鱼际穴治疗哮喘急性发作临床观察</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>李素荷</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>T1 인체 임상관찰(비RCT, LU6+LU10)</t>
+          <t>종합</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>71.2</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>75</v>
+      </c>
+      <c r="O6" t="n">
+        <v>68.8</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>예</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>ARI v3.0 | ARI-Core 71.2 ± 0 (B) | SI 75 | 잠정 가중치 0.40/0.35/0.25 | 민감도(등가중치): 68.8 (C, 등급 변동 → 가중치 민감)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
-        <v>1679</v>
-      </c>
-      <c r="B7" t="n">
-        <v>2009</v>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>참고(Target 제외)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>泽田 공최(《针灸真髓》 1941, 尺泽下二寸) — 2026-10-04 채점 기록, 2026-10-25 Target 제외 규칙에 따라 판정에서 철회, 이중 채점 대상 아님</t>
+        </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>J Altern Complement Med</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Characteristics of electrical skin resistance at acupuncture points in healthy humans.</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Kramer S, Winterhalter K, Schober G, Becker U, Wiegele B, Kutz DF et al.</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>19422323</t>
-        </is>
+          <t>S_orig</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>50</v>
+      </c>
+      <c r="E7" t="n">
+        <v>50</v>
+      </c>
+      <c r="F7" t="n">
+        <v>50</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>10.1089/acm.2008.0331</t>
+          <t>25/25/75/75</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>T1 보조(인체 피부저항)</t>
+          <t>25/25/75/75</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
-        <v>1807</v>
-      </c>
-      <c r="B8" t="n">
-        <v>2025</v>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>참고(Target 제외)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>泽田 공최(《针灸真髓》 1941, 尺泽下二寸) — 2026-10-04 채점 기록, 2026-10-25 Target 제외 규칙에 따라 판정에서 철회, 이중 채점 대상 아님</t>
+        </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Annals of Medicine</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Effect of press needle stimulation on postoperative pulmonary complications in video-assisted thoracoscopic surgery patients: a randomized controlled trial</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Jing Tan, Yong Dong Feng, Hui Liu, Yihu Zhou, Jiaqin Cai, Yueyi Jiang et al.</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>40953233</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>10.1080/07853890.2025.2560684</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>T1 보조(인체 RCT, 다혈)</t>
-        </is>
+          <t>S_clarity</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>25</v>
+      </c>
+      <c r="E8" t="n">
+        <v>25</v>
+      </c>
+      <c r="F8" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
-        <v>17</v>
-      </c>
-      <c r="B9" t="n">
-        <v>2002</v>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>참고(Target 제외)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>泽田 공최(《针灸真髓》 1941, 尺泽下二寸) — 2026-10-04 채점 기록, 2026-10-25 Target 제외 규칙에 따라 판정에서 철회, 이중 채점 대상 아님</t>
+        </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Neuroscience Letters</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Unique Immunomodulation by Electro-acupuncture in Humans Possibly via Stimulation of the Autonomic Nervous System</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Mori H</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>B-Check ⑥ 참고만(다혈, LU6 특이성 미확인)</t>
-        </is>
+          <t>S_reflex</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>25</v>
+      </c>
+      <c r="E9" t="n">
+        <v>25</v>
+      </c>
+      <c r="F9" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="n">
-        <v>1561</v>
-      </c>
-      <c r="B10" t="n">
-        <v>2011</v>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>참고(Target 제외)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>泽田 공최(《针灸真髓》 1941, 尺泽下二寸) — 2026-10-04 채점 기록, 2026-10-25 Target 제외 규칙에 따라 판정에서 철회, 이중 채점 대상 아님</t>
+        </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>中医文献杂志</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>“孔最治痔”讹传及其对当代针灸学的影响</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>黄幼民 黄龙祥</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>반증: 孔最治痔 讹传</t>
-        </is>
+          <t>S_safety</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>50</v>
+      </c>
+      <c r="E10" t="n">
+        <v>50</v>
+      </c>
+      <c r="F10" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="n">
-        <v>1563</v>
-      </c>
-      <c r="B11" t="n">
-        <v>2011</v>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>참고(Target 제외)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>泽田 공최(《针灸真髓》 1941, 尺泽下二寸) — 2026-10-04 채점 기록, 2026-10-25 Target 제외 규칙에 따라 판정에서 철회, 이중 채점 대상 아님</t>
+        </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>针刺研究</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>“孔最治痔”的讹传及其对当代针灸学的影响</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>黄幼民 黄龙祥</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>반증: 孔最治痔 讹传</t>
+          <t>종합</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>게이트1(S_orig 또는 S_clarity &lt; 50 → 최고 C); 게이트2(경혈 특이 Layer A 0편 → S_reflex ≤ 25, H)</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>35</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>D·H</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>50</v>
+      </c>
+      <c r="O11" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>아니오</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>ARI v3.0 | ARI-Core 35 ± 0 (D·H) | SI 50 | 잠정 가중치 0.40/0.35/0.25 | 민감도(등가중치): 33.3 (D, 등급 불변)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="n">
-        <v>1723</v>
-      </c>
-      <c r="B12" t="n">
-        <v>2011</v>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>판정</t>
+        </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>针刺研究</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>孔最治痔的讹传及其对当代针灸学的影响</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>黄幼民</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>반증: 1563 별도 소장본</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>1564</v>
-      </c>
-      <c r="B13" t="n">
-        <v>2012</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>科学通报</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>从三个著名案例看针灸临床研究的复杂性</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>黄龙祥 黄幼民</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>10.1360/972011-743</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>반증: 비특이 효과 해석</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>461</v>
-      </c>
-      <c r="B14" t="n">
-        <v>2021</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Korean Journal of Acupuncture</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>공최(LU6)를 활용한 치질치료의 근거에 대한 문헌고찰</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>조은별</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>10.14406/acu.2021.024</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>T2 문헌고찰</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>1742</v>
-      </c>
-      <c r="B15" t="n">
-        <v>2018</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>World Journal of Acupuncture-Moxibustion</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Acupuncture at Kongzui (LU6) for 76 cases of hemorrhoids</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Li XY</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>T2 증례군</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>1808</v>
-      </c>
-      <c r="B16" t="n">
-        <v>2021</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Journal of Agromedicine and Medical Sciences</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>The Effectiveness of Acupuncture Therapy in Patient with Hemorrhoid: A Case Report</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Fieka Meitaqwatiningarum, Christina Lanny Simadibrata, Irma Nareswari</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>10.19184/ams.v7i3.23937</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>T2 증례보고</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>제외</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>17·795·1458·1461·1002·1678은 구판에서 실증 근거로 나열됐으나 LU6 기전 근거가 아니어서 제외(17은 참고 표기만)</t>
+          <t>단일 Target(표준 공최 Target 1≡2≡3, 71.2 ± 0 B) — 분기·우위 판정 없음. 구 ΔARI 36.2(표준 vs 泽田) 비교는 2026-10-25 Target 제외 규칙에 따라 철회</t>
         </is>
       </c>
     </row>
@@ -3921,267 +4341,540 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>일시</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="B1" s="3" t="inlineStr">
         <is>
-          <t>소스</t>
+          <t>항목</t>
         </is>
       </c>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>HTTP</t>
+          <t>채점자 A</t>
         </is>
       </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
-          <t>수집</t>
+          <t>채점자 B</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>중복제거</t>
+          <t>최종</t>
         </is>
       </c>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>신규</t>
+          <t>Layer B 참조 ID</t>
         </is>
       </c>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>쿼리</t>
+          <t>papers.id</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>근거 요지(A)</t>
+        </is>
+      </c>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>근거 요지(B)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-04T09:51:32</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>pubmed</t>
-        </is>
+          <t>T1≡2≡3</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>200</v>
+        <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>9</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="E2" t="n">
+        <v>2</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>B1-01, B1-03, B2-02, B2-09, B2-10</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>("LU6" OR "Kongzui" OR "孔最") AND (acupuncture OR electroacupuncture) AND (nerve OR reflex OR autonomic OR mechanism OR anatomy)</t>
+          <t>1806</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>2대 교재 모두 가쪽아래팔피부신경·노신경 얕은가지·노동정맥·노쪽피부정맥을 명시하고, 혈위 특이 초음파 실측(1806)이 있음</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2대 교재 구조 일치 + LU6 특이 초음파 실측(1806)으로 자침층 실체 확인</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-04T09:51:32</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>openalex</t>
-        </is>
+          <t>T1≡2≡3</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>200</v>
+        <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>16</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>doi_starts_with:10.13703,title_and_abstract.search:"Kongzui" OR "LU6" | doi_starts_with:10.13702,… | has_doi:true,…</t>
+          <t>B1-02, B1-03, B3-01, B3-20</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>피절 C5–C6(가쪽아래팔피부신경)은 폐의 교감 내장절(T1–T5)과 직접 맞지 않아 간접·유추 수준</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>피절 C5–C7(가쪽아래팔피부신경·노신경) vs 폐 내장절 T1–T5·미주 — 직접 분절 정합 아님, 유추 수준. 보고서의 2점은 근거 없음</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-04T09:51:32</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>crossref</t>
-        </is>
+          <t>T1≡2≡3</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>200</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>B3-05, B3-06</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Kongzui acupuncture nerve reflex</t>
+          <t>1682</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>구심 섬유형은 일반 동물 기전에서 유추한 것이며 LU6 특이 구심 섬유 연구는 없음. B3-17(ST36 PROKR2)은 범위 밖</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>LU6 구심 섬유형·수용체 실측 없음, 일반 체계 유추</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-04T09:51:32</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>T1≡2≡3</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>25</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>B3-04, B3-05</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>체성-자율 반사의 상척수 경로를 유추. LU6에서 NTS·미주 경로를 확인한 연구 없음</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>중추 경로(NTS 등) LU6 특이 근거 없음, 유추</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-23T21:44:38</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>pubmed</t>
-        </is>
+          <t>T1≡2≡3</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>200</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>9</v>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>B3-05</t>
+        </is>
+      </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>("LU6" OR "Kongzui" OR "孔最") AND (acupuncture OR electroacupuncture) AND (nerve OR reflex OR autonomic OR mechanism OR anatomy) | ("LU6" OR "Kongzui" OR "孔最") AND ("Zhongguo Zhen Jiu"[Journal] OR "Zhen Ci Yan Jiu"[Journal])</t>
+          <t>1682, 1683, 1684</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>천식 쥐에서 기도평활근 이완(β2-AR, ET-1)으로 고전 주치 '咳逆'(동인)과 방향이 같으나, 동물·짝혈 연구임. 《明堂》 원주치 '汗不出'(발한)에 대한 원심 기전 근거는 없음</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>쥐 천식 모델에서 기도평활근 이완(咳逆·气喘 방향 일치)이나 동물·LU10 배합 한정. 명당경 단독 주치(热病汗不出)와의 기전 연결은 없음. 보고서의 2점은 과대</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-23T21:44:38</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>openalex</t>
-        </is>
+          <t>T1≡2≡3</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>200</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>16</v>
-      </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>B4-03, B4-04, B4-05</t>
+        </is>
+      </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>doi_starts_with:10.13703,title_and_abstract.search:"Kongzui" OR "LU6" | doi_starts_with:10.13702,title_and_abstract.search:"Kongzui" OR "LU6" | has_doi:true,title_and_abstract.search:"Kongzui" OR "LU6" AND (acupuncture OR electroacupuncture)</t>
+          <t>17, 1679, 1726, 1807</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>인체 연구는 다혈 조합에서만 있고 LU6 단독 효과는 분리되지 않음</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>비RCT 임상관찰·피부저항 측정 수준, 혈위 특이성 반증(B4-05) 병기 필요</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-23T21:44:38</t>
+          <t>T1≡2≡3</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>crossref</t>
+          <t>합계</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>200</v>
+        <v>7</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Kongzui acupuncture nerve reflex</t>
+        <v>7</v>
+      </c>
+      <c r="E8" t="n">
+        <v>7</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>판정: 미부합</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-23T21:44:38</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
+          <t>참고(Target 제외, 채점 기록만)</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>25</v>
-      </c>
-      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>B1-01, B1-03</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>규범 해부로 위팔노근·노신경 분지 부위를 추정할 뿐이며 교재와 실측 근거가 없음</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>교재·실측 없음, 규범 해부서 유추만</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>참고(Target 제외, 채점 기록만)</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2</v>
+      </c>
+      <c r="C10" t="n">
         <v>0</v>
       </c>
-      <c r="G9" t="inlineStr"/>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>B1-03, B3-01</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>C5–C6 피절과 항문직장(S2–S4, T10–L2 자율 분절) 사이에 분절 대응이 없음. 사와다의 '肺络于大肠' 경락 논리만 있음</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>피절 C5–C7 vs 항문·직장 S2–S4(하부 T10–L2 교감) — 분절 정합 부재. 泽田의 '肺络大肠' 경락 논리 외 근거 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>참고(Target 제외, 채점 기록만)</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>3</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>B3-06</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>일반 구심 섬유형에서 유추한 것뿐임</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>일반 구심 섬유 유추</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>참고(Target 제외, 채점 기록만)</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>4</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>B3-07, B3-08</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>강자극에 의한 DNIC·관문조절 같은 비특이 진통 경로로만 설명 가능</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>강자극 비특이 진통(DNIC)으로 유추 가능, 혈위 특이 경로 아님</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>참고(Target 제외, 채점 기록만)</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>5</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>B3-05, B4-05</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>치핵 혈류나 항문괄약근으로 가는 원심 경로 근거가 없음. 《通考》는 비특이 효과라고 반론함</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>고전 단독 주치에 치질 없음(《通考》), 원심 효과 방향 근거 부재</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>참고(Target 제외, 채점 기록만)</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>6</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>B4-04, B4-05</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>1742, 1808</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>인체 증례와 증례군 보고만 있고 대조군이 없으며 취혈 위치가 불명확함</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>증례군·증례보고 수준, 비특이성 반증(B4-05, papers.id 1564) 병존</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>참고(Target 제외, 채점 기록만)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>합계</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>4</v>
+      </c>
+      <c r="D15" t="n">
+        <v>4</v>
+      </c>
+      <c r="E15" t="n">
+        <v>4</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>판정: 가설</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
